--- a/jpcore-r4/feature/BodySiteに関するTerminologyの見直し/ValueSet-jp-imagingstudy-radiology-bodysite-vs.xlsx
+++ b/jpcore-r4/feature/BodySiteに関するTerminologyの見直し/ValueSet-jp-imagingstudy-radiology-bodysite-vs.xlsx
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>検査の対象となる身体部位のコード</t>
+    <t>放射線検査画像の対象となる身体部位のコード</t>
   </si>
   <si>
     <t>Purpose</t>
